--- a/resources/templates/standard/L1100-20.xlsx
+++ b/resources/templates/standard/L1100-20.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="32">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>※ 주/1회 (금요일) 시업 종료 후 작성 할 것.</t>
   </si>
@@ -1181,7 +1184,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1293,7 +1298,7 @@
     <row r="3" ht="60" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -1728,16 +1733,16 @@
       <c r="AV10" s="3"/>
       <c r="AW10" s="3"/>
       <c r="AX10" s="11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY10" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ10" s="12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA10" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" ht="20.15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -1963,7 +1968,7 @@
     <row r="15" ht="17.15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -1977,7 +1982,7 @@
       <c r="L15" s="14"/>
       <c r="M15" s="8"/>
       <c r="N15" s="15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
@@ -2022,13 +2027,13 @@
     <row r="16" ht="17.15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
       <c r="F16" s="17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -2081,13 +2086,13 @@
     <row r="17" ht="17.15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
       <c r="F17" s="17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="17"/>
@@ -2140,13 +2145,13 @@
     <row r="18" ht="17.15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -2199,13 +2204,13 @@
     <row r="19" ht="17.15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
@@ -2258,13 +2263,13 @@
     <row r="20" ht="17.15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="20"/>
       <c r="E20" s="20"/>
       <c r="F20" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
@@ -2498,14 +2503,14 @@
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
       <c r="R24" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S24" s="24"/>
       <c r="T24" s="24"/>
       <c r="U24" s="24"/>
       <c r="V24" s="24"/>
       <c r="W24" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X24" s="25"/>
       <c r="Y24" s="25"/>
@@ -2706,16 +2711,16 @@
     <row r="28" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C28" s="27"/>
       <c r="D28" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
       <c r="G28" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H28" s="27"/>
       <c r="I28" s="27"/>
@@ -2724,7 +2729,7 @@
       <c r="L28" s="27"/>
       <c r="M28" s="27"/>
       <c r="N28" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O28" s="28"/>
       <c r="P28" s="28"/>
@@ -2733,7 +2738,7 @@
       <c r="S28" s="28"/>
       <c r="T28" s="28"/>
       <c r="U28" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V28" s="29"/>
       <c r="W28" s="29"/>
@@ -2743,7 +2748,7 @@
       <c r="AA28" s="29"/>
       <c r="AB28" s="29"/>
       <c r="AC28" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD28" s="28"/>
       <c r="AE28" s="28"/>
@@ -2777,7 +2782,7 @@
       </c>
       <c r="C29" s="30"/>
       <c r="D29" s="31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29" s="31"/>
       <c r="F29" s="31"/>
@@ -2836,7 +2841,7 @@
       </c>
       <c r="C30" s="36"/>
       <c r="D30" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="19"/>
@@ -2895,7 +2900,7 @@
       </c>
       <c r="C31" s="36"/>
       <c r="D31" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="19"/>
       <c r="F31" s="19"/>
@@ -2954,7 +2959,7 @@
       </c>
       <c r="C32" s="36"/>
       <c r="D32" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E32" s="19"/>
       <c r="F32" s="19"/>
@@ -3013,7 +3018,7 @@
       </c>
       <c r="C33" s="39"/>
       <c r="D33" s="40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E33" s="40"/>
       <c r="F33" s="40"/>
@@ -3128,7 +3133,7 @@
       <c r="E35" s="43"/>
       <c r="F35" s="43"/>
       <c r="G35" s="44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H35" s="44"/>
       <c r="I35" s="44"/>
@@ -3144,7 +3149,7 @@
       <c r="S35" s="44"/>
       <c r="T35" s="44"/>
       <c r="U35" s="44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V35" s="44"/>
       <c r="W35" s="44"/>
@@ -3182,16 +3187,16 @@
     <row r="36" ht="15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C36" s="27"/>
       <c r="D36" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E36" s="28"/>
       <c r="F36" s="28"/>
       <c r="G36" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H36" s="27"/>
       <c r="I36" s="27"/>
@@ -3200,7 +3205,7 @@
       <c r="L36" s="27"/>
       <c r="M36" s="27"/>
       <c r="N36" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O36" s="28"/>
       <c r="P36" s="28"/>
@@ -3209,7 +3214,7 @@
       <c r="S36" s="28"/>
       <c r="T36" s="28"/>
       <c r="U36" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V36" s="29"/>
       <c r="W36" s="29"/>
@@ -3219,7 +3224,7 @@
       <c r="AA36" s="29"/>
       <c r="AB36" s="29"/>
       <c r="AC36" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD36" s="28"/>
       <c r="AE36" s="28"/>
@@ -3253,7 +3258,7 @@
       </c>
       <c r="C37" s="30"/>
       <c r="D37" s="31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37" s="31"/>
       <c r="F37" s="31"/>
@@ -3312,7 +3317,7 @@
       </c>
       <c r="C38" s="36"/>
       <c r="D38" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E38" s="19"/>
       <c r="F38" s="19"/>
@@ -3371,7 +3376,7 @@
       </c>
       <c r="C39" s="36"/>
       <c r="D39" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E39" s="19"/>
       <c r="F39" s="19"/>
@@ -3430,7 +3435,7 @@
       </c>
       <c r="C40" s="36"/>
       <c r="D40" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
@@ -3489,7 +3494,7 @@
       </c>
       <c r="C41" s="39"/>
       <c r="D41" s="40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E41" s="40"/>
       <c r="F41" s="40"/>
@@ -3599,7 +3604,7 @@
     <row r="43" ht="20.15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C43" s="45"/>
       <c r="D43" s="45"/>
@@ -3656,7 +3661,7 @@
     <row r="44" ht="17.15" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="46"/>
